--- a/jogos_2025-06-24.xlsx
+++ b/jogos_2025-06-24.xlsx
@@ -643,16 +643,16 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.65</v>
+        <v>1.92</v>
       </c>
       <c r="M2" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="N2" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="O2" t="n">
-        <v>3.25</v>
+        <v>2.26</v>
       </c>
       <c r="P2" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="U2" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="V2" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.65</v>
+        <v>2.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['77', '90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45832.52083333334</v>
@@ -772,16 +772,16 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.92</v>
+        <v>2.65</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="O3" t="n">
-        <v>2.26</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="R3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['77', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH3" t="n">
         <v>1.25</v>
       </c>
-      <c r="S3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T3" t="n">
+      <c r="AI3" t="n">
         <v>2.2</v>
       </c>
-      <c r="U3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>['45']</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AJ3" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45832.52083333334</v>
